--- a/Blue_Ribbon_BSC_Sample_Data.xlsx
+++ b/Blue_Ribbon_BSC_Sample_Data.xlsx
@@ -685,7 +685,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -778,6 +778,18 @@
       <c r="B8" s="3" t="inlineStr">
         <is>
           <t>Manual sample RAG: &lt;=0 = Green, &gt;0 to 3 = Amber, &gt;3 = Red. This is demo logic only and is not an agreed Blue Ribbon threshold.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="32" customHeight="1">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>Vacancies %</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>Synthetic service-level vacancy percentage. Starter RAG thresholds are &lt;=5% Green, &gt;5%-10% Amber, &gt;10% Red.</t>
         </is>
       </c>
     </row>
@@ -1307,7 +1319,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1897"/>
+  <dimension ref="A1:H2041"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -59997,6 +60009,4902 @@
         </is>
       </c>
       <c r="H1897" s="7" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+    </row>
+    <row r="1898">
+      <c r="A1898" s="12" t="n">
+        <v>45901</v>
+      </c>
+      <c r="B1898" s="7" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="C1898" s="7" t="inlineStr">
+        <is>
+          <t>BEAU</t>
+        </is>
+      </c>
+      <c r="D1898" s="7" t="inlineStr">
+        <is>
+          <t>VACANCY_PCT</t>
+        </is>
+      </c>
+      <c r="E1898" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F1898" s="7" t="n"/>
+      <c r="G1898" s="7" t="inlineStr">
+        <is>
+          <t>Synthetic vacancy percentage example</t>
+        </is>
+      </c>
+      <c r="H1898" s="7" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+    </row>
+    <row r="1899">
+      <c r="A1899" s="12" t="n">
+        <v>45901</v>
+      </c>
+      <c r="B1899" s="7" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="C1899" s="7" t="inlineStr">
+        <is>
+          <t>BOLD</t>
+        </is>
+      </c>
+      <c r="D1899" s="7" t="inlineStr">
+        <is>
+          <t>VACANCY_PCT</t>
+        </is>
+      </c>
+      <c r="E1899" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F1899" s="7" t="n"/>
+      <c r="G1899" s="7" t="inlineStr">
+        <is>
+          <t>Synthetic vacancy percentage example</t>
+        </is>
+      </c>
+      <c r="H1899" s="7" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+    </row>
+    <row r="1900">
+      <c r="A1900" s="12" t="n">
+        <v>45901</v>
+      </c>
+      <c r="B1900" s="7" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="C1900" s="7" t="inlineStr">
+        <is>
+          <t>CHELFORD</t>
+        </is>
+      </c>
+      <c r="D1900" s="7" t="inlineStr">
+        <is>
+          <t>VACANCY_PCT</t>
+        </is>
+      </c>
+      <c r="E1900" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="F1900" s="7" t="n"/>
+      <c r="G1900" s="7" t="inlineStr">
+        <is>
+          <t>Synthetic vacancy percentage example</t>
+        </is>
+      </c>
+      <c r="H1900" s="7" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+    </row>
+    <row r="1901">
+      <c r="A1901" s="12" t="n">
+        <v>45901</v>
+      </c>
+      <c r="B1901" s="7" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="C1901" s="7" t="inlineStr">
+        <is>
+          <t>CHURCH</t>
+        </is>
+      </c>
+      <c r="D1901" s="7" t="inlineStr">
+        <is>
+          <t>VACANCY_PCT</t>
+        </is>
+      </c>
+      <c r="E1901" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="F1901" s="7" t="n"/>
+      <c r="G1901" s="7" t="inlineStr">
+        <is>
+          <t>Synthetic vacancy percentage example</t>
+        </is>
+      </c>
+      <c r="H1901" s="7" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+    </row>
+    <row r="1902">
+      <c r="A1902" s="12" t="n">
+        <v>45901</v>
+      </c>
+      <c r="B1902" s="7" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="C1902" s="7" t="inlineStr">
+        <is>
+          <t>HAWKSWORTH</t>
+        </is>
+      </c>
+      <c r="D1902" s="7" t="inlineStr">
+        <is>
+          <t>VACANCY_PCT</t>
+        </is>
+      </c>
+      <c r="E1902" s="7" t="n">
+        <v>14</v>
+      </c>
+      <c r="F1902" s="7" t="n"/>
+      <c r="G1902" s="7" t="inlineStr">
+        <is>
+          <t>Synthetic vacancy percentage example</t>
+        </is>
+      </c>
+      <c r="H1902" s="7" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+    </row>
+    <row r="1903">
+      <c r="A1903" s="12" t="n">
+        <v>45901</v>
+      </c>
+      <c r="B1903" s="7" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="C1903" s="7" t="inlineStr">
+        <is>
+          <t>MILLBROOK</t>
+        </is>
+      </c>
+      <c r="D1903" s="7" t="inlineStr">
+        <is>
+          <t>VACANCY_PCT</t>
+        </is>
+      </c>
+      <c r="E1903" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1903" s="7" t="n"/>
+      <c r="G1903" s="7" t="inlineStr">
+        <is>
+          <t>Synthetic vacancy percentage example</t>
+        </is>
+      </c>
+      <c r="H1903" s="7" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+    </row>
+    <row r="1904">
+      <c r="A1904" s="12" t="n">
+        <v>45901</v>
+      </c>
+      <c r="B1904" s="7" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="C1904" s="7" t="inlineStr">
+        <is>
+          <t>RAVEN</t>
+        </is>
+      </c>
+      <c r="D1904" s="7" t="inlineStr">
+        <is>
+          <t>VACANCY_PCT</t>
+        </is>
+      </c>
+      <c r="E1904" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="F1904" s="7" t="n"/>
+      <c r="G1904" s="7" t="inlineStr">
+        <is>
+          <t>Synthetic vacancy percentage example</t>
+        </is>
+      </c>
+      <c r="H1904" s="7" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+    </row>
+    <row r="1905">
+      <c r="A1905" s="12" t="n">
+        <v>45901</v>
+      </c>
+      <c r="B1905" s="7" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="C1905" s="7" t="inlineStr">
+        <is>
+          <t>RIVERSIDE</t>
+        </is>
+      </c>
+      <c r="D1905" s="7" t="inlineStr">
+        <is>
+          <t>VACANCY_PCT</t>
+        </is>
+      </c>
+      <c r="E1905" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="F1905" s="7" t="n"/>
+      <c r="G1905" s="7" t="inlineStr">
+        <is>
+          <t>Synthetic vacancy percentage example</t>
+        </is>
+      </c>
+      <c r="H1905" s="7" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+    </row>
+    <row r="1906">
+      <c r="A1906" s="12" t="n">
+        <v>45901</v>
+      </c>
+      <c r="B1906" s="7" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="C1906" s="7" t="inlineStr">
+        <is>
+          <t>RYECROFT</t>
+        </is>
+      </c>
+      <c r="D1906" s="7" t="inlineStr">
+        <is>
+          <t>VACANCY_PCT</t>
+        </is>
+      </c>
+      <c r="E1906" s="7" t="n">
+        <v>13</v>
+      </c>
+      <c r="F1906" s="7" t="n"/>
+      <c r="G1906" s="7" t="inlineStr">
+        <is>
+          <t>Synthetic vacancy percentage example</t>
+        </is>
+      </c>
+      <c r="H1906" s="7" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+    </row>
+    <row r="1907">
+      <c r="A1907" s="12" t="n">
+        <v>45901</v>
+      </c>
+      <c r="B1907" s="7" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="C1907" s="7" t="inlineStr">
+        <is>
+          <t>SEREN</t>
+        </is>
+      </c>
+      <c r="D1907" s="7" t="inlineStr">
+        <is>
+          <t>VACANCY_PCT</t>
+        </is>
+      </c>
+      <c r="E1907" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="F1907" s="7" t="n"/>
+      <c r="G1907" s="7" t="inlineStr">
+        <is>
+          <t>Synthetic vacancy percentage example</t>
+        </is>
+      </c>
+      <c r="H1907" s="7" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+    </row>
+    <row r="1908">
+      <c r="A1908" s="12" t="n">
+        <v>45901</v>
+      </c>
+      <c r="B1908" s="7" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="C1908" s="7" t="inlineStr">
+        <is>
+          <t>SYCAMORE</t>
+        </is>
+      </c>
+      <c r="D1908" s="7" t="inlineStr">
+        <is>
+          <t>VACANCY_PCT</t>
+        </is>
+      </c>
+      <c r="E1908" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="F1908" s="7" t="n"/>
+      <c r="G1908" s="7" t="inlineStr">
+        <is>
+          <t>Synthetic vacancy percentage example</t>
+        </is>
+      </c>
+      <c r="H1908" s="7" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+    </row>
+    <row r="1909">
+      <c r="A1909" s="12" t="n">
+        <v>45901</v>
+      </c>
+      <c r="B1909" s="7" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="C1909" s="7" t="inlineStr">
+        <is>
+          <t>WILLOW</t>
+        </is>
+      </c>
+      <c r="D1909" s="7" t="inlineStr">
+        <is>
+          <t>VACANCY_PCT</t>
+        </is>
+      </c>
+      <c r="E1909" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="F1909" s="7" t="n"/>
+      <c r="G1909" s="7" t="inlineStr">
+        <is>
+          <t>Synthetic vacancy percentage example</t>
+        </is>
+      </c>
+      <c r="H1909" s="7" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+    </row>
+    <row r="1910">
+      <c r="A1910" s="12" t="n">
+        <v>45931</v>
+      </c>
+      <c r="B1910" s="7" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="C1910" s="7" t="inlineStr">
+        <is>
+          <t>BEAU</t>
+        </is>
+      </c>
+      <c r="D1910" s="7" t="inlineStr">
+        <is>
+          <t>VACANCY_PCT</t>
+        </is>
+      </c>
+      <c r="E1910" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1910" s="7" t="n"/>
+      <c r="G1910" s="7" t="inlineStr">
+        <is>
+          <t>Synthetic vacancy percentage example</t>
+        </is>
+      </c>
+      <c r="H1910" s="7" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+    </row>
+    <row r="1911">
+      <c r="A1911" s="12" t="n">
+        <v>45931</v>
+      </c>
+      <c r="B1911" s="7" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="C1911" s="7" t="inlineStr">
+        <is>
+          <t>BOLD</t>
+        </is>
+      </c>
+      <c r="D1911" s="7" t="inlineStr">
+        <is>
+          <t>VACANCY_PCT</t>
+        </is>
+      </c>
+      <c r="E1911" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="F1911" s="7" t="n"/>
+      <c r="G1911" s="7" t="inlineStr">
+        <is>
+          <t>Synthetic vacancy percentage example</t>
+        </is>
+      </c>
+      <c r="H1911" s="7" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+    </row>
+    <row r="1912">
+      <c r="A1912" s="12" t="n">
+        <v>45931</v>
+      </c>
+      <c r="B1912" s="7" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="C1912" s="7" t="inlineStr">
+        <is>
+          <t>CHELFORD</t>
+        </is>
+      </c>
+      <c r="D1912" s="7" t="inlineStr">
+        <is>
+          <t>VACANCY_PCT</t>
+        </is>
+      </c>
+      <c r="E1912" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="F1912" s="7" t="n"/>
+      <c r="G1912" s="7" t="inlineStr">
+        <is>
+          <t>Synthetic vacancy percentage example</t>
+        </is>
+      </c>
+      <c r="H1912" s="7" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+    </row>
+    <row r="1913">
+      <c r="A1913" s="12" t="n">
+        <v>45931</v>
+      </c>
+      <c r="B1913" s="7" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="C1913" s="7" t="inlineStr">
+        <is>
+          <t>CHURCH</t>
+        </is>
+      </c>
+      <c r="D1913" s="7" t="inlineStr">
+        <is>
+          <t>VACANCY_PCT</t>
+        </is>
+      </c>
+      <c r="E1913" s="7" t="n">
+        <v>13</v>
+      </c>
+      <c r="F1913" s="7" t="n"/>
+      <c r="G1913" s="7" t="inlineStr">
+        <is>
+          <t>Synthetic vacancy percentage example</t>
+        </is>
+      </c>
+      <c r="H1913" s="7" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+    </row>
+    <row r="1914">
+      <c r="A1914" s="12" t="n">
+        <v>45931</v>
+      </c>
+      <c r="B1914" s="7" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="C1914" s="7" t="inlineStr">
+        <is>
+          <t>HAWKSWORTH</t>
+        </is>
+      </c>
+      <c r="D1914" s="7" t="inlineStr">
+        <is>
+          <t>VACANCY_PCT</t>
+        </is>
+      </c>
+      <c r="E1914" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="F1914" s="7" t="n"/>
+      <c r="G1914" s="7" t="inlineStr">
+        <is>
+          <t>Synthetic vacancy percentage example</t>
+        </is>
+      </c>
+      <c r="H1914" s="7" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+    </row>
+    <row r="1915">
+      <c r="A1915" s="12" t="n">
+        <v>45931</v>
+      </c>
+      <c r="B1915" s="7" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="C1915" s="7" t="inlineStr">
+        <is>
+          <t>MILLBROOK</t>
+        </is>
+      </c>
+      <c r="D1915" s="7" t="inlineStr">
+        <is>
+          <t>VACANCY_PCT</t>
+        </is>
+      </c>
+      <c r="E1915" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="F1915" s="7" t="n"/>
+      <c r="G1915" s="7" t="inlineStr">
+        <is>
+          <t>Synthetic vacancy percentage example</t>
+        </is>
+      </c>
+      <c r="H1915" s="7" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+    </row>
+    <row r="1916">
+      <c r="A1916" s="12" t="n">
+        <v>45931</v>
+      </c>
+      <c r="B1916" s="7" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="C1916" s="7" t="inlineStr">
+        <is>
+          <t>RAVEN</t>
+        </is>
+      </c>
+      <c r="D1916" s="7" t="inlineStr">
+        <is>
+          <t>VACANCY_PCT</t>
+        </is>
+      </c>
+      <c r="E1916" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="F1916" s="7" t="n"/>
+      <c r="G1916" s="7" t="inlineStr">
+        <is>
+          <t>Synthetic vacancy percentage example</t>
+        </is>
+      </c>
+      <c r="H1916" s="7" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+    </row>
+    <row r="1917">
+      <c r="A1917" s="12" t="n">
+        <v>45931</v>
+      </c>
+      <c r="B1917" s="7" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="C1917" s="7" t="inlineStr">
+        <is>
+          <t>RIVERSIDE</t>
+        </is>
+      </c>
+      <c r="D1917" s="7" t="inlineStr">
+        <is>
+          <t>VACANCY_PCT</t>
+        </is>
+      </c>
+      <c r="E1917" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="F1917" s="7" t="n"/>
+      <c r="G1917" s="7" t="inlineStr">
+        <is>
+          <t>Synthetic vacancy percentage example</t>
+        </is>
+      </c>
+      <c r="H1917" s="7" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+    </row>
+    <row r="1918">
+      <c r="A1918" s="12" t="n">
+        <v>45931</v>
+      </c>
+      <c r="B1918" s="7" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="C1918" s="7" t="inlineStr">
+        <is>
+          <t>RYECROFT</t>
+        </is>
+      </c>
+      <c r="D1918" s="7" t="inlineStr">
+        <is>
+          <t>VACANCY_PCT</t>
+        </is>
+      </c>
+      <c r="E1918" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F1918" s="7" t="n"/>
+      <c r="G1918" s="7" t="inlineStr">
+        <is>
+          <t>Synthetic vacancy percentage example</t>
+        </is>
+      </c>
+      <c r="H1918" s="7" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+    </row>
+    <row r="1919">
+      <c r="A1919" s="12" t="n">
+        <v>45931</v>
+      </c>
+      <c r="B1919" s="7" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="C1919" s="7" t="inlineStr">
+        <is>
+          <t>SEREN</t>
+        </is>
+      </c>
+      <c r="D1919" s="7" t="inlineStr">
+        <is>
+          <t>VACANCY_PCT</t>
+        </is>
+      </c>
+      <c r="E1919" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F1919" s="7" t="n"/>
+      <c r="G1919" s="7" t="inlineStr">
+        <is>
+          <t>Synthetic vacancy percentage example</t>
+        </is>
+      </c>
+      <c r="H1919" s="7" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+    </row>
+    <row r="1920">
+      <c r="A1920" s="12" t="n">
+        <v>45931</v>
+      </c>
+      <c r="B1920" s="7" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="C1920" s="7" t="inlineStr">
+        <is>
+          <t>SYCAMORE</t>
+        </is>
+      </c>
+      <c r="D1920" s="7" t="inlineStr">
+        <is>
+          <t>VACANCY_PCT</t>
+        </is>
+      </c>
+      <c r="E1920" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="F1920" s="7" t="n"/>
+      <c r="G1920" s="7" t="inlineStr">
+        <is>
+          <t>Synthetic vacancy percentage example</t>
+        </is>
+      </c>
+      <c r="H1920" s="7" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+    </row>
+    <row r="1921">
+      <c r="A1921" s="12" t="n">
+        <v>45931</v>
+      </c>
+      <c r="B1921" s="7" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="C1921" s="7" t="inlineStr">
+        <is>
+          <t>WILLOW</t>
+        </is>
+      </c>
+      <c r="D1921" s="7" t="inlineStr">
+        <is>
+          <t>VACANCY_PCT</t>
+        </is>
+      </c>
+      <c r="E1921" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="F1921" s="7" t="n"/>
+      <c r="G1921" s="7" t="inlineStr">
+        <is>
+          <t>Synthetic vacancy percentage example</t>
+        </is>
+      </c>
+      <c r="H1921" s="7" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+    </row>
+    <row r="1922">
+      <c r="A1922" s="12" t="n">
+        <v>45962</v>
+      </c>
+      <c r="B1922" s="7" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="C1922" s="7" t="inlineStr">
+        <is>
+          <t>BEAU</t>
+        </is>
+      </c>
+      <c r="D1922" s="7" t="inlineStr">
+        <is>
+          <t>VACANCY_PCT</t>
+        </is>
+      </c>
+      <c r="E1922" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="F1922" s="7" t="n"/>
+      <c r="G1922" s="7" t="inlineStr">
+        <is>
+          <t>Synthetic vacancy percentage example</t>
+        </is>
+      </c>
+      <c r="H1922" s="7" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+    </row>
+    <row r="1923">
+      <c r="A1923" s="12" t="n">
+        <v>45962</v>
+      </c>
+      <c r="B1923" s="7" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="C1923" s="7" t="inlineStr">
+        <is>
+          <t>BOLD</t>
+        </is>
+      </c>
+      <c r="D1923" s="7" t="inlineStr">
+        <is>
+          <t>VACANCY_PCT</t>
+        </is>
+      </c>
+      <c r="E1923" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="F1923" s="7" t="n"/>
+      <c r="G1923" s="7" t="inlineStr">
+        <is>
+          <t>Synthetic vacancy percentage example</t>
+        </is>
+      </c>
+      <c r="H1923" s="7" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+    </row>
+    <row r="1924">
+      <c r="A1924" s="12" t="n">
+        <v>45962</v>
+      </c>
+      <c r="B1924" s="7" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="C1924" s="7" t="inlineStr">
+        <is>
+          <t>CHELFORD</t>
+        </is>
+      </c>
+      <c r="D1924" s="7" t="inlineStr">
+        <is>
+          <t>VACANCY_PCT</t>
+        </is>
+      </c>
+      <c r="E1924" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="F1924" s="7" t="n"/>
+      <c r="G1924" s="7" t="inlineStr">
+        <is>
+          <t>Synthetic vacancy percentage example</t>
+        </is>
+      </c>
+      <c r="H1924" s="7" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+    </row>
+    <row r="1925">
+      <c r="A1925" s="12" t="n">
+        <v>45962</v>
+      </c>
+      <c r="B1925" s="7" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="C1925" s="7" t="inlineStr">
+        <is>
+          <t>CHURCH</t>
+        </is>
+      </c>
+      <c r="D1925" s="7" t="inlineStr">
+        <is>
+          <t>VACANCY_PCT</t>
+        </is>
+      </c>
+      <c r="E1925" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F1925" s="7" t="n"/>
+      <c r="G1925" s="7" t="inlineStr">
+        <is>
+          <t>Synthetic vacancy percentage example</t>
+        </is>
+      </c>
+      <c r="H1925" s="7" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+    </row>
+    <row r="1926">
+      <c r="A1926" s="12" t="n">
+        <v>45962</v>
+      </c>
+      <c r="B1926" s="7" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="C1926" s="7" t="inlineStr">
+        <is>
+          <t>HAWKSWORTH</t>
+        </is>
+      </c>
+      <c r="D1926" s="7" t="inlineStr">
+        <is>
+          <t>VACANCY_PCT</t>
+        </is>
+      </c>
+      <c r="E1926" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F1926" s="7" t="n"/>
+      <c r="G1926" s="7" t="inlineStr">
+        <is>
+          <t>Synthetic vacancy percentage example</t>
+        </is>
+      </c>
+      <c r="H1926" s="7" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+    </row>
+    <row r="1927">
+      <c r="A1927" s="12" t="n">
+        <v>45962</v>
+      </c>
+      <c r="B1927" s="7" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="C1927" s="7" t="inlineStr">
+        <is>
+          <t>MILLBROOK</t>
+        </is>
+      </c>
+      <c r="D1927" s="7" t="inlineStr">
+        <is>
+          <t>VACANCY_PCT</t>
+        </is>
+      </c>
+      <c r="E1927" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="F1927" s="7" t="n"/>
+      <c r="G1927" s="7" t="inlineStr">
+        <is>
+          <t>Synthetic vacancy percentage example</t>
+        </is>
+      </c>
+      <c r="H1927" s="7" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+    </row>
+    <row r="1928">
+      <c r="A1928" s="12" t="n">
+        <v>45962</v>
+      </c>
+      <c r="B1928" s="7" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="C1928" s="7" t="inlineStr">
+        <is>
+          <t>RAVEN</t>
+        </is>
+      </c>
+      <c r="D1928" s="7" t="inlineStr">
+        <is>
+          <t>VACANCY_PCT</t>
+        </is>
+      </c>
+      <c r="E1928" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="F1928" s="7" t="n"/>
+      <c r="G1928" s="7" t="inlineStr">
+        <is>
+          <t>Synthetic vacancy percentage example</t>
+        </is>
+      </c>
+      <c r="H1928" s="7" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+    </row>
+    <row r="1929">
+      <c r="A1929" s="12" t="n">
+        <v>45962</v>
+      </c>
+      <c r="B1929" s="7" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="C1929" s="7" t="inlineStr">
+        <is>
+          <t>RIVERSIDE</t>
+        </is>
+      </c>
+      <c r="D1929" s="7" t="inlineStr">
+        <is>
+          <t>VACANCY_PCT</t>
+        </is>
+      </c>
+      <c r="E1929" s="7" t="n">
+        <v>14</v>
+      </c>
+      <c r="F1929" s="7" t="n"/>
+      <c r="G1929" s="7" t="inlineStr">
+        <is>
+          <t>Synthetic vacancy percentage example</t>
+        </is>
+      </c>
+      <c r="H1929" s="7" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+    </row>
+    <row r="1930">
+      <c r="A1930" s="12" t="n">
+        <v>45962</v>
+      </c>
+      <c r="B1930" s="7" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="C1930" s="7" t="inlineStr">
+        <is>
+          <t>RYECROFT</t>
+        </is>
+      </c>
+      <c r="D1930" s="7" t="inlineStr">
+        <is>
+          <t>VACANCY_PCT</t>
+        </is>
+      </c>
+      <c r="E1930" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1930" s="7" t="n"/>
+      <c r="G1930" s="7" t="inlineStr">
+        <is>
+          <t>Synthetic vacancy percentage example</t>
+        </is>
+      </c>
+      <c r="H1930" s="7" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+    </row>
+    <row r="1931">
+      <c r="A1931" s="12" t="n">
+        <v>45962</v>
+      </c>
+      <c r="B1931" s="7" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="C1931" s="7" t="inlineStr">
+        <is>
+          <t>SEREN</t>
+        </is>
+      </c>
+      <c r="D1931" s="7" t="inlineStr">
+        <is>
+          <t>VACANCY_PCT</t>
+        </is>
+      </c>
+      <c r="E1931" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="F1931" s="7" t="n"/>
+      <c r="G1931" s="7" t="inlineStr">
+        <is>
+          <t>Synthetic vacancy percentage example</t>
+        </is>
+      </c>
+      <c r="H1931" s="7" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+    </row>
+    <row r="1932">
+      <c r="A1932" s="12" t="n">
+        <v>45962</v>
+      </c>
+      <c r="B1932" s="7" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="C1932" s="7" t="inlineStr">
+        <is>
+          <t>SYCAMORE</t>
+        </is>
+      </c>
+      <c r="D1932" s="7" t="inlineStr">
+        <is>
+          <t>VACANCY_PCT</t>
+        </is>
+      </c>
+      <c r="E1932" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="F1932" s="7" t="n"/>
+      <c r="G1932" s="7" t="inlineStr">
+        <is>
+          <t>Synthetic vacancy percentage example</t>
+        </is>
+      </c>
+      <c r="H1932" s="7" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+    </row>
+    <row r="1933">
+      <c r="A1933" s="12" t="n">
+        <v>45962</v>
+      </c>
+      <c r="B1933" s="7" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="C1933" s="7" t="inlineStr">
+        <is>
+          <t>WILLOW</t>
+        </is>
+      </c>
+      <c r="D1933" s="7" t="inlineStr">
+        <is>
+          <t>VACANCY_PCT</t>
+        </is>
+      </c>
+      <c r="E1933" s="7" t="n">
+        <v>13</v>
+      </c>
+      <c r="F1933" s="7" t="n"/>
+      <c r="G1933" s="7" t="inlineStr">
+        <is>
+          <t>Synthetic vacancy percentage example</t>
+        </is>
+      </c>
+      <c r="H1933" s="7" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+    </row>
+    <row r="1934">
+      <c r="A1934" s="12" t="n">
+        <v>45992</v>
+      </c>
+      <c r="B1934" s="7" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="C1934" s="7" t="inlineStr">
+        <is>
+          <t>BEAU</t>
+        </is>
+      </c>
+      <c r="D1934" s="7" t="inlineStr">
+        <is>
+          <t>VACANCY_PCT</t>
+        </is>
+      </c>
+      <c r="E1934" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="F1934" s="7" t="n"/>
+      <c r="G1934" s="7" t="inlineStr">
+        <is>
+          <t>Synthetic vacancy percentage example</t>
+        </is>
+      </c>
+      <c r="H1934" s="7" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+    </row>
+    <row r="1935">
+      <c r="A1935" s="12" t="n">
+        <v>45992</v>
+      </c>
+      <c r="B1935" s="7" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="C1935" s="7" t="inlineStr">
+        <is>
+          <t>BOLD</t>
+        </is>
+      </c>
+      <c r="D1935" s="7" t="inlineStr">
+        <is>
+          <t>VACANCY_PCT</t>
+        </is>
+      </c>
+      <c r="E1935" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="F1935" s="7" t="n"/>
+      <c r="G1935" s="7" t="inlineStr">
+        <is>
+          <t>Synthetic vacancy percentage example</t>
+        </is>
+      </c>
+      <c r="H1935" s="7" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+    </row>
+    <row r="1936">
+      <c r="A1936" s="12" t="n">
+        <v>45992</v>
+      </c>
+      <c r="B1936" s="7" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="C1936" s="7" t="inlineStr">
+        <is>
+          <t>CHELFORD</t>
+        </is>
+      </c>
+      <c r="D1936" s="7" t="inlineStr">
+        <is>
+          <t>VACANCY_PCT</t>
+        </is>
+      </c>
+      <c r="E1936" s="7" t="n">
+        <v>14</v>
+      </c>
+      <c r="F1936" s="7" t="n"/>
+      <c r="G1936" s="7" t="inlineStr">
+        <is>
+          <t>Synthetic vacancy percentage example</t>
+        </is>
+      </c>
+      <c r="H1936" s="7" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+    </row>
+    <row r="1937">
+      <c r="A1937" s="12" t="n">
+        <v>45992</v>
+      </c>
+      <c r="B1937" s="7" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="C1937" s="7" t="inlineStr">
+        <is>
+          <t>CHURCH</t>
+        </is>
+      </c>
+      <c r="D1937" s="7" t="inlineStr">
+        <is>
+          <t>VACANCY_PCT</t>
+        </is>
+      </c>
+      <c r="E1937" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1937" s="7" t="n"/>
+      <c r="G1937" s="7" t="inlineStr">
+        <is>
+          <t>Synthetic vacancy percentage example</t>
+        </is>
+      </c>
+      <c r="H1937" s="7" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+    </row>
+    <row r="1938">
+      <c r="A1938" s="12" t="n">
+        <v>45992</v>
+      </c>
+      <c r="B1938" s="7" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="C1938" s="7" t="inlineStr">
+        <is>
+          <t>HAWKSWORTH</t>
+        </is>
+      </c>
+      <c r="D1938" s="7" t="inlineStr">
+        <is>
+          <t>VACANCY_PCT</t>
+        </is>
+      </c>
+      <c r="E1938" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="F1938" s="7" t="n"/>
+      <c r="G1938" s="7" t="inlineStr">
+        <is>
+          <t>Synthetic vacancy percentage example</t>
+        </is>
+      </c>
+      <c r="H1938" s="7" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+    </row>
+    <row r="1939">
+      <c r="A1939" s="12" t="n">
+        <v>45992</v>
+      </c>
+      <c r="B1939" s="7" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="C1939" s="7" t="inlineStr">
+        <is>
+          <t>MILLBROOK</t>
+        </is>
+      </c>
+      <c r="D1939" s="7" t="inlineStr">
+        <is>
+          <t>VACANCY_PCT</t>
+        </is>
+      </c>
+      <c r="E1939" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="F1939" s="7" t="n"/>
+      <c r="G1939" s="7" t="inlineStr">
+        <is>
+          <t>Synthetic vacancy percentage example</t>
+        </is>
+      </c>
+      <c r="H1939" s="7" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+    </row>
+    <row r="1940">
+      <c r="A1940" s="12" t="n">
+        <v>45992</v>
+      </c>
+      <c r="B1940" s="7" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="C1940" s="7" t="inlineStr">
+        <is>
+          <t>RAVEN</t>
+        </is>
+      </c>
+      <c r="D1940" s="7" t="inlineStr">
+        <is>
+          <t>VACANCY_PCT</t>
+        </is>
+      </c>
+      <c r="E1940" s="7" t="n">
+        <v>13</v>
+      </c>
+      <c r="F1940" s="7" t="n"/>
+      <c r="G1940" s="7" t="inlineStr">
+        <is>
+          <t>Synthetic vacancy percentage example</t>
+        </is>
+      </c>
+      <c r="H1940" s="7" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+    </row>
+    <row r="1941">
+      <c r="A1941" s="12" t="n">
+        <v>45992</v>
+      </c>
+      <c r="B1941" s="7" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="C1941" s="7" t="inlineStr">
+        <is>
+          <t>RIVERSIDE</t>
+        </is>
+      </c>
+      <c r="D1941" s="7" t="inlineStr">
+        <is>
+          <t>VACANCY_PCT</t>
+        </is>
+      </c>
+      <c r="E1941" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="F1941" s="7" t="n"/>
+      <c r="G1941" s="7" t="inlineStr">
+        <is>
+          <t>Synthetic vacancy percentage example</t>
+        </is>
+      </c>
+      <c r="H1941" s="7" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+    </row>
+    <row r="1942">
+      <c r="A1942" s="12" t="n">
+        <v>45992</v>
+      </c>
+      <c r="B1942" s="7" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="C1942" s="7" t="inlineStr">
+        <is>
+          <t>RYECROFT</t>
+        </is>
+      </c>
+      <c r="D1942" s="7" t="inlineStr">
+        <is>
+          <t>VACANCY_PCT</t>
+        </is>
+      </c>
+      <c r="E1942" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="F1942" s="7" t="n"/>
+      <c r="G1942" s="7" t="inlineStr">
+        <is>
+          <t>Synthetic vacancy percentage example</t>
+        </is>
+      </c>
+      <c r="H1942" s="7" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+    </row>
+    <row r="1943">
+      <c r="A1943" s="12" t="n">
+        <v>45992</v>
+      </c>
+      <c r="B1943" s="7" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="C1943" s="7" t="inlineStr">
+        <is>
+          <t>SEREN</t>
+        </is>
+      </c>
+      <c r="D1943" s="7" t="inlineStr">
+        <is>
+          <t>VACANCY_PCT</t>
+        </is>
+      </c>
+      <c r="E1943" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="F1943" s="7" t="n"/>
+      <c r="G1943" s="7" t="inlineStr">
+        <is>
+          <t>Synthetic vacancy percentage example</t>
+        </is>
+      </c>
+      <c r="H1943" s="7" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+    </row>
+    <row r="1944">
+      <c r="A1944" s="12" t="n">
+        <v>45992</v>
+      </c>
+      <c r="B1944" s="7" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="C1944" s="7" t="inlineStr">
+        <is>
+          <t>SYCAMORE</t>
+        </is>
+      </c>
+      <c r="D1944" s="7" t="inlineStr">
+        <is>
+          <t>VACANCY_PCT</t>
+        </is>
+      </c>
+      <c r="E1944" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="F1944" s="7" t="n"/>
+      <c r="G1944" s="7" t="inlineStr">
+        <is>
+          <t>Synthetic vacancy percentage example</t>
+        </is>
+      </c>
+      <c r="H1944" s="7" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+    </row>
+    <row r="1945">
+      <c r="A1945" s="12" t="n">
+        <v>45992</v>
+      </c>
+      <c r="B1945" s="7" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="C1945" s="7" t="inlineStr">
+        <is>
+          <t>WILLOW</t>
+        </is>
+      </c>
+      <c r="D1945" s="7" t="inlineStr">
+        <is>
+          <t>VACANCY_PCT</t>
+        </is>
+      </c>
+      <c r="E1945" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F1945" s="7" t="n"/>
+      <c r="G1945" s="7" t="inlineStr">
+        <is>
+          <t>Synthetic vacancy percentage example</t>
+        </is>
+      </c>
+      <c r="H1945" s="7" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+    </row>
+    <row r="1946">
+      <c r="A1946" s="12" t="n">
+        <v>46023</v>
+      </c>
+      <c r="B1946" s="7" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="C1946" s="7" t="inlineStr">
+        <is>
+          <t>BEAU</t>
+        </is>
+      </c>
+      <c r="D1946" s="7" t="inlineStr">
+        <is>
+          <t>VACANCY_PCT</t>
+        </is>
+      </c>
+      <c r="E1946" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="F1946" s="7" t="n"/>
+      <c r="G1946" s="7" t="inlineStr">
+        <is>
+          <t>Synthetic vacancy percentage example</t>
+        </is>
+      </c>
+      <c r="H1946" s="7" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+    </row>
+    <row r="1947">
+      <c r="A1947" s="12" t="n">
+        <v>46023</v>
+      </c>
+      <c r="B1947" s="7" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="C1947" s="7" t="inlineStr">
+        <is>
+          <t>BOLD</t>
+        </is>
+      </c>
+      <c r="D1947" s="7" t="inlineStr">
+        <is>
+          <t>VACANCY_PCT</t>
+        </is>
+      </c>
+      <c r="E1947" s="7" t="n">
+        <v>13</v>
+      </c>
+      <c r="F1947" s="7" t="n"/>
+      <c r="G1947" s="7" t="inlineStr">
+        <is>
+          <t>Synthetic vacancy percentage example</t>
+        </is>
+      </c>
+      <c r="H1947" s="7" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+    </row>
+    <row r="1948">
+      <c r="A1948" s="12" t="n">
+        <v>46023</v>
+      </c>
+      <c r="B1948" s="7" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="C1948" s="7" t="inlineStr">
+        <is>
+          <t>CHELFORD</t>
+        </is>
+      </c>
+      <c r="D1948" s="7" t="inlineStr">
+        <is>
+          <t>VACANCY_PCT</t>
+        </is>
+      </c>
+      <c r="E1948" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="F1948" s="7" t="n"/>
+      <c r="G1948" s="7" t="inlineStr">
+        <is>
+          <t>Synthetic vacancy percentage example</t>
+        </is>
+      </c>
+      <c r="H1948" s="7" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+    </row>
+    <row r="1949">
+      <c r="A1949" s="12" t="n">
+        <v>46023</v>
+      </c>
+      <c r="B1949" s="7" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="C1949" s="7" t="inlineStr">
+        <is>
+          <t>CHURCH</t>
+        </is>
+      </c>
+      <c r="D1949" s="7" t="inlineStr">
+        <is>
+          <t>VACANCY_PCT</t>
+        </is>
+      </c>
+      <c r="E1949" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="F1949" s="7" t="n"/>
+      <c r="G1949" s="7" t="inlineStr">
+        <is>
+          <t>Synthetic vacancy percentage example</t>
+        </is>
+      </c>
+      <c r="H1949" s="7" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+    </row>
+    <row r="1950">
+      <c r="A1950" s="12" t="n">
+        <v>46023</v>
+      </c>
+      <c r="B1950" s="7" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="C1950" s="7" t="inlineStr">
+        <is>
+          <t>HAWKSWORTH</t>
+        </is>
+      </c>
+      <c r="D1950" s="7" t="inlineStr">
+        <is>
+          <t>VACANCY_PCT</t>
+        </is>
+      </c>
+      <c r="E1950" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="F1950" s="7" t="n"/>
+      <c r="G1950" s="7" t="inlineStr">
+        <is>
+          <t>Synthetic vacancy percentage example</t>
+        </is>
+      </c>
+      <c r="H1950" s="7" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+    </row>
+    <row r="1951">
+      <c r="A1951" s="12" t="n">
+        <v>46023</v>
+      </c>
+      <c r="B1951" s="7" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="C1951" s="7" t="inlineStr">
+        <is>
+          <t>MILLBROOK</t>
+        </is>
+      </c>
+      <c r="D1951" s="7" t="inlineStr">
+        <is>
+          <t>VACANCY_PCT</t>
+        </is>
+      </c>
+      <c r="E1951" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="F1951" s="7" t="n"/>
+      <c r="G1951" s="7" t="inlineStr">
+        <is>
+          <t>Synthetic vacancy percentage example</t>
+        </is>
+      </c>
+      <c r="H1951" s="7" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+    </row>
+    <row r="1952">
+      <c r="A1952" s="12" t="n">
+        <v>46023</v>
+      </c>
+      <c r="B1952" s="7" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="C1952" s="7" t="inlineStr">
+        <is>
+          <t>RAVEN</t>
+        </is>
+      </c>
+      <c r="D1952" s="7" t="inlineStr">
+        <is>
+          <t>VACANCY_PCT</t>
+        </is>
+      </c>
+      <c r="E1952" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F1952" s="7" t="n"/>
+      <c r="G1952" s="7" t="inlineStr">
+        <is>
+          <t>Synthetic vacancy percentage example</t>
+        </is>
+      </c>
+      <c r="H1952" s="7" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+    </row>
+    <row r="1953">
+      <c r="A1953" s="12" t="n">
+        <v>46023</v>
+      </c>
+      <c r="B1953" s="7" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="C1953" s="7" t="inlineStr">
+        <is>
+          <t>RIVERSIDE</t>
+        </is>
+      </c>
+      <c r="D1953" s="7" t="inlineStr">
+        <is>
+          <t>VACANCY_PCT</t>
+        </is>
+      </c>
+      <c r="E1953" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F1953" s="7" t="n"/>
+      <c r="G1953" s="7" t="inlineStr">
+        <is>
+          <t>Synthetic vacancy percentage example</t>
+        </is>
+      </c>
+      <c r="H1953" s="7" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+    </row>
+    <row r="1954">
+      <c r="A1954" s="12" t="n">
+        <v>46023</v>
+      </c>
+      <c r="B1954" s="7" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="C1954" s="7" t="inlineStr">
+        <is>
+          <t>RYECROFT</t>
+        </is>
+      </c>
+      <c r="D1954" s="7" t="inlineStr">
+        <is>
+          <t>VACANCY_PCT</t>
+        </is>
+      </c>
+      <c r="E1954" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="F1954" s="7" t="n"/>
+      <c r="G1954" s="7" t="inlineStr">
+        <is>
+          <t>Synthetic vacancy percentage example</t>
+        </is>
+      </c>
+      <c r="H1954" s="7" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+    </row>
+    <row r="1955">
+      <c r="A1955" s="12" t="n">
+        <v>46023</v>
+      </c>
+      <c r="B1955" s="7" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="C1955" s="7" t="inlineStr">
+        <is>
+          <t>SEREN</t>
+        </is>
+      </c>
+      <c r="D1955" s="7" t="inlineStr">
+        <is>
+          <t>VACANCY_PCT</t>
+        </is>
+      </c>
+      <c r="E1955" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="F1955" s="7" t="n"/>
+      <c r="G1955" s="7" t="inlineStr">
+        <is>
+          <t>Synthetic vacancy percentage example</t>
+        </is>
+      </c>
+      <c r="H1955" s="7" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+    </row>
+    <row r="1956">
+      <c r="A1956" s="12" t="n">
+        <v>46023</v>
+      </c>
+      <c r="B1956" s="7" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="C1956" s="7" t="inlineStr">
+        <is>
+          <t>SYCAMORE</t>
+        </is>
+      </c>
+      <c r="D1956" s="7" t="inlineStr">
+        <is>
+          <t>VACANCY_PCT</t>
+        </is>
+      </c>
+      <c r="E1956" s="7" t="n">
+        <v>14</v>
+      </c>
+      <c r="F1956" s="7" t="n"/>
+      <c r="G1956" s="7" t="inlineStr">
+        <is>
+          <t>Synthetic vacancy percentage example</t>
+        </is>
+      </c>
+      <c r="H1956" s="7" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+    </row>
+    <row r="1957">
+      <c r="A1957" s="12" t="n">
+        <v>46023</v>
+      </c>
+      <c r="B1957" s="7" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="C1957" s="7" t="inlineStr">
+        <is>
+          <t>WILLOW</t>
+        </is>
+      </c>
+      <c r="D1957" s="7" t="inlineStr">
+        <is>
+          <t>VACANCY_PCT</t>
+        </is>
+      </c>
+      <c r="E1957" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1957" s="7" t="n"/>
+      <c r="G1957" s="7" t="inlineStr">
+        <is>
+          <t>Synthetic vacancy percentage example</t>
+        </is>
+      </c>
+      <c r="H1957" s="7" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+    </row>
+    <row r="1958">
+      <c r="A1958" s="12" t="n">
+        <v>46054</v>
+      </c>
+      <c r="B1958" s="7" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="C1958" s="7" t="inlineStr">
+        <is>
+          <t>BEAU</t>
+        </is>
+      </c>
+      <c r="D1958" s="7" t="inlineStr">
+        <is>
+          <t>VACANCY_PCT</t>
+        </is>
+      </c>
+      <c r="E1958" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="F1958" s="7" t="n"/>
+      <c r="G1958" s="7" t="inlineStr">
+        <is>
+          <t>Synthetic vacancy percentage example</t>
+        </is>
+      </c>
+      <c r="H1958" s="7" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+    </row>
+    <row r="1959">
+      <c r="A1959" s="12" t="n">
+        <v>46054</v>
+      </c>
+      <c r="B1959" s="7" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="C1959" s="7" t="inlineStr">
+        <is>
+          <t>BOLD</t>
+        </is>
+      </c>
+      <c r="D1959" s="7" t="inlineStr">
+        <is>
+          <t>VACANCY_PCT</t>
+        </is>
+      </c>
+      <c r="E1959" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F1959" s="7" t="n"/>
+      <c r="G1959" s="7" t="inlineStr">
+        <is>
+          <t>Synthetic vacancy percentage example</t>
+        </is>
+      </c>
+      <c r="H1959" s="7" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+    </row>
+    <row r="1960">
+      <c r="A1960" s="12" t="n">
+        <v>46054</v>
+      </c>
+      <c r="B1960" s="7" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="C1960" s="7" t="inlineStr">
+        <is>
+          <t>CHELFORD</t>
+        </is>
+      </c>
+      <c r="D1960" s="7" t="inlineStr">
+        <is>
+          <t>VACANCY_PCT</t>
+        </is>
+      </c>
+      <c r="E1960" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F1960" s="7" t="n"/>
+      <c r="G1960" s="7" t="inlineStr">
+        <is>
+          <t>Synthetic vacancy percentage example</t>
+        </is>
+      </c>
+      <c r="H1960" s="7" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+    </row>
+    <row r="1961">
+      <c r="A1961" s="12" t="n">
+        <v>46054</v>
+      </c>
+      <c r="B1961" s="7" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="C1961" s="7" t="inlineStr">
+        <is>
+          <t>CHURCH</t>
+        </is>
+      </c>
+      <c r="D1961" s="7" t="inlineStr">
+        <is>
+          <t>VACANCY_PCT</t>
+        </is>
+      </c>
+      <c r="E1961" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="F1961" s="7" t="n"/>
+      <c r="G1961" s="7" t="inlineStr">
+        <is>
+          <t>Synthetic vacancy percentage example</t>
+        </is>
+      </c>
+      <c r="H1961" s="7" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+    </row>
+    <row r="1962">
+      <c r="A1962" s="12" t="n">
+        <v>46054</v>
+      </c>
+      <c r="B1962" s="7" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="C1962" s="7" t="inlineStr">
+        <is>
+          <t>HAWKSWORTH</t>
+        </is>
+      </c>
+      <c r="D1962" s="7" t="inlineStr">
+        <is>
+          <t>VACANCY_PCT</t>
+        </is>
+      </c>
+      <c r="E1962" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="F1962" s="7" t="n"/>
+      <c r="G1962" s="7" t="inlineStr">
+        <is>
+          <t>Synthetic vacancy percentage example</t>
+        </is>
+      </c>
+      <c r="H1962" s="7" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+    </row>
+    <row r="1963">
+      <c r="A1963" s="12" t="n">
+        <v>46054</v>
+      </c>
+      <c r="B1963" s="7" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="C1963" s="7" t="inlineStr">
+        <is>
+          <t>MILLBROOK</t>
+        </is>
+      </c>
+      <c r="D1963" s="7" t="inlineStr">
+        <is>
+          <t>VACANCY_PCT</t>
+        </is>
+      </c>
+      <c r="E1963" s="7" t="n">
+        <v>14</v>
+      </c>
+      <c r="F1963" s="7" t="n"/>
+      <c r="G1963" s="7" t="inlineStr">
+        <is>
+          <t>Synthetic vacancy percentage example</t>
+        </is>
+      </c>
+      <c r="H1963" s="7" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+    </row>
+    <row r="1964">
+      <c r="A1964" s="12" t="n">
+        <v>46054</v>
+      </c>
+      <c r="B1964" s="7" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="C1964" s="7" t="inlineStr">
+        <is>
+          <t>RAVEN</t>
+        </is>
+      </c>
+      <c r="D1964" s="7" t="inlineStr">
+        <is>
+          <t>VACANCY_PCT</t>
+        </is>
+      </c>
+      <c r="E1964" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1964" s="7" t="n"/>
+      <c r="G1964" s="7" t="inlineStr">
+        <is>
+          <t>Synthetic vacancy percentage example</t>
+        </is>
+      </c>
+      <c r="H1964" s="7" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+    </row>
+    <row r="1965">
+      <c r="A1965" s="12" t="n">
+        <v>46054</v>
+      </c>
+      <c r="B1965" s="7" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="C1965" s="7" t="inlineStr">
+        <is>
+          <t>RIVERSIDE</t>
+        </is>
+      </c>
+      <c r="D1965" s="7" t="inlineStr">
+        <is>
+          <t>VACANCY_PCT</t>
+        </is>
+      </c>
+      <c r="E1965" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="F1965" s="7" t="n"/>
+      <c r="G1965" s="7" t="inlineStr">
+        <is>
+          <t>Synthetic vacancy percentage example</t>
+        </is>
+      </c>
+      <c r="H1965" s="7" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+    </row>
+    <row r="1966">
+      <c r="A1966" s="12" t="n">
+        <v>46054</v>
+      </c>
+      <c r="B1966" s="7" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="C1966" s="7" t="inlineStr">
+        <is>
+          <t>RYECROFT</t>
+        </is>
+      </c>
+      <c r="D1966" s="7" t="inlineStr">
+        <is>
+          <t>VACANCY_PCT</t>
+        </is>
+      </c>
+      <c r="E1966" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="F1966" s="7" t="n"/>
+      <c r="G1966" s="7" t="inlineStr">
+        <is>
+          <t>Synthetic vacancy percentage example</t>
+        </is>
+      </c>
+      <c r="H1966" s="7" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+    </row>
+    <row r="1967">
+      <c r="A1967" s="12" t="n">
+        <v>46054</v>
+      </c>
+      <c r="B1967" s="7" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="C1967" s="7" t="inlineStr">
+        <is>
+          <t>SEREN</t>
+        </is>
+      </c>
+      <c r="D1967" s="7" t="inlineStr">
+        <is>
+          <t>VACANCY_PCT</t>
+        </is>
+      </c>
+      <c r="E1967" s="7" t="n">
+        <v>13</v>
+      </c>
+      <c r="F1967" s="7" t="n"/>
+      <c r="G1967" s="7" t="inlineStr">
+        <is>
+          <t>Synthetic vacancy percentage example</t>
+        </is>
+      </c>
+      <c r="H1967" s="7" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+    </row>
+    <row r="1968">
+      <c r="A1968" s="12" t="n">
+        <v>46054</v>
+      </c>
+      <c r="B1968" s="7" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="C1968" s="7" t="inlineStr">
+        <is>
+          <t>SYCAMORE</t>
+        </is>
+      </c>
+      <c r="D1968" s="7" t="inlineStr">
+        <is>
+          <t>VACANCY_PCT</t>
+        </is>
+      </c>
+      <c r="E1968" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="F1968" s="7" t="n"/>
+      <c r="G1968" s="7" t="inlineStr">
+        <is>
+          <t>Synthetic vacancy percentage example</t>
+        </is>
+      </c>
+      <c r="H1968" s="7" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+    </row>
+    <row r="1969">
+      <c r="A1969" s="12" t="n">
+        <v>46054</v>
+      </c>
+      <c r="B1969" s="7" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="C1969" s="7" t="inlineStr">
+        <is>
+          <t>WILLOW</t>
+        </is>
+      </c>
+      <c r="D1969" s="7" t="inlineStr">
+        <is>
+          <t>VACANCY_PCT</t>
+        </is>
+      </c>
+      <c r="E1969" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="F1969" s="7" t="n"/>
+      <c r="G1969" s="7" t="inlineStr">
+        <is>
+          <t>Synthetic vacancy percentage example</t>
+        </is>
+      </c>
+      <c r="H1969" s="7" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+    </row>
+    <row r="1970">
+      <c r="A1970" s="12" t="n">
+        <v>46082</v>
+      </c>
+      <c r="B1970" s="7" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="C1970" s="7" t="inlineStr">
+        <is>
+          <t>BEAU</t>
+        </is>
+      </c>
+      <c r="D1970" s="7" t="inlineStr">
+        <is>
+          <t>VACANCY_PCT</t>
+        </is>
+      </c>
+      <c r="E1970" s="7" t="n">
+        <v>14</v>
+      </c>
+      <c r="F1970" s="7" t="n"/>
+      <c r="G1970" s="7" t="inlineStr">
+        <is>
+          <t>Synthetic vacancy percentage example</t>
+        </is>
+      </c>
+      <c r="H1970" s="7" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+    </row>
+    <row r="1971">
+      <c r="A1971" s="12" t="n">
+        <v>46082</v>
+      </c>
+      <c r="B1971" s="7" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="C1971" s="7" t="inlineStr">
+        <is>
+          <t>BOLD</t>
+        </is>
+      </c>
+      <c r="D1971" s="7" t="inlineStr">
+        <is>
+          <t>VACANCY_PCT</t>
+        </is>
+      </c>
+      <c r="E1971" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1971" s="7" t="n"/>
+      <c r="G1971" s="7" t="inlineStr">
+        <is>
+          <t>Synthetic vacancy percentage example</t>
+        </is>
+      </c>
+      <c r="H1971" s="7" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+    </row>
+    <row r="1972">
+      <c r="A1972" s="12" t="n">
+        <v>46082</v>
+      </c>
+      <c r="B1972" s="7" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="C1972" s="7" t="inlineStr">
+        <is>
+          <t>CHELFORD</t>
+        </is>
+      </c>
+      <c r="D1972" s="7" t="inlineStr">
+        <is>
+          <t>VACANCY_PCT</t>
+        </is>
+      </c>
+      <c r="E1972" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="F1972" s="7" t="n"/>
+      <c r="G1972" s="7" t="inlineStr">
+        <is>
+          <t>Synthetic vacancy percentage example</t>
+        </is>
+      </c>
+      <c r="H1972" s="7" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+    </row>
+    <row r="1973">
+      <c r="A1973" s="12" t="n">
+        <v>46082</v>
+      </c>
+      <c r="B1973" s="7" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="C1973" s="7" t="inlineStr">
+        <is>
+          <t>CHURCH</t>
+        </is>
+      </c>
+      <c r="D1973" s="7" t="inlineStr">
+        <is>
+          <t>VACANCY_PCT</t>
+        </is>
+      </c>
+      <c r="E1973" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="F1973" s="7" t="n"/>
+      <c r="G1973" s="7" t="inlineStr">
+        <is>
+          <t>Synthetic vacancy percentage example</t>
+        </is>
+      </c>
+      <c r="H1973" s="7" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+    </row>
+    <row r="1974">
+      <c r="A1974" s="12" t="n">
+        <v>46082</v>
+      </c>
+      <c r="B1974" s="7" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="C1974" s="7" t="inlineStr">
+        <is>
+          <t>HAWKSWORTH</t>
+        </is>
+      </c>
+      <c r="D1974" s="7" t="inlineStr">
+        <is>
+          <t>VACANCY_PCT</t>
+        </is>
+      </c>
+      <c r="E1974" s="7" t="n">
+        <v>13</v>
+      </c>
+      <c r="F1974" s="7" t="n"/>
+      <c r="G1974" s="7" t="inlineStr">
+        <is>
+          <t>Synthetic vacancy percentage example</t>
+        </is>
+      </c>
+      <c r="H1974" s="7" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+    </row>
+    <row r="1975">
+      <c r="A1975" s="12" t="n">
+        <v>46082</v>
+      </c>
+      <c r="B1975" s="7" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="C1975" s="7" t="inlineStr">
+        <is>
+          <t>MILLBROOK</t>
+        </is>
+      </c>
+      <c r="D1975" s="7" t="inlineStr">
+        <is>
+          <t>VACANCY_PCT</t>
+        </is>
+      </c>
+      <c r="E1975" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="F1975" s="7" t="n"/>
+      <c r="G1975" s="7" t="inlineStr">
+        <is>
+          <t>Synthetic vacancy percentage example</t>
+        </is>
+      </c>
+      <c r="H1975" s="7" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+    </row>
+    <row r="1976">
+      <c r="A1976" s="12" t="n">
+        <v>46082</v>
+      </c>
+      <c r="B1976" s="7" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="C1976" s="7" t="inlineStr">
+        <is>
+          <t>RAVEN</t>
+        </is>
+      </c>
+      <c r="D1976" s="7" t="inlineStr">
+        <is>
+          <t>VACANCY_PCT</t>
+        </is>
+      </c>
+      <c r="E1976" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="F1976" s="7" t="n"/>
+      <c r="G1976" s="7" t="inlineStr">
+        <is>
+          <t>Synthetic vacancy percentage example</t>
+        </is>
+      </c>
+      <c r="H1976" s="7" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+    </row>
+    <row r="1977">
+      <c r="A1977" s="12" t="n">
+        <v>46082</v>
+      </c>
+      <c r="B1977" s="7" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="C1977" s="7" t="inlineStr">
+        <is>
+          <t>RIVERSIDE</t>
+        </is>
+      </c>
+      <c r="D1977" s="7" t="inlineStr">
+        <is>
+          <t>VACANCY_PCT</t>
+        </is>
+      </c>
+      <c r="E1977" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="F1977" s="7" t="n"/>
+      <c r="G1977" s="7" t="inlineStr">
+        <is>
+          <t>Synthetic vacancy percentage example</t>
+        </is>
+      </c>
+      <c r="H1977" s="7" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+    </row>
+    <row r="1978">
+      <c r="A1978" s="12" t="n">
+        <v>46082</v>
+      </c>
+      <c r="B1978" s="7" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="C1978" s="7" t="inlineStr">
+        <is>
+          <t>RYECROFT</t>
+        </is>
+      </c>
+      <c r="D1978" s="7" t="inlineStr">
+        <is>
+          <t>VACANCY_PCT</t>
+        </is>
+      </c>
+      <c r="E1978" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="F1978" s="7" t="n"/>
+      <c r="G1978" s="7" t="inlineStr">
+        <is>
+          <t>Synthetic vacancy percentage example</t>
+        </is>
+      </c>
+      <c r="H1978" s="7" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+    </row>
+    <row r="1979">
+      <c r="A1979" s="12" t="n">
+        <v>46082</v>
+      </c>
+      <c r="B1979" s="7" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="C1979" s="7" t="inlineStr">
+        <is>
+          <t>SEREN</t>
+        </is>
+      </c>
+      <c r="D1979" s="7" t="inlineStr">
+        <is>
+          <t>VACANCY_PCT</t>
+        </is>
+      </c>
+      <c r="E1979" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F1979" s="7" t="n"/>
+      <c r="G1979" s="7" t="inlineStr">
+        <is>
+          <t>Synthetic vacancy percentage example</t>
+        </is>
+      </c>
+      <c r="H1979" s="7" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+    </row>
+    <row r="1980">
+      <c r="A1980" s="12" t="n">
+        <v>46082</v>
+      </c>
+      <c r="B1980" s="7" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="C1980" s="7" t="inlineStr">
+        <is>
+          <t>SYCAMORE</t>
+        </is>
+      </c>
+      <c r="D1980" s="7" t="inlineStr">
+        <is>
+          <t>VACANCY_PCT</t>
+        </is>
+      </c>
+      <c r="E1980" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F1980" s="7" t="n"/>
+      <c r="G1980" s="7" t="inlineStr">
+        <is>
+          <t>Synthetic vacancy percentage example</t>
+        </is>
+      </c>
+      <c r="H1980" s="7" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+    </row>
+    <row r="1981">
+      <c r="A1981" s="12" t="n">
+        <v>46082</v>
+      </c>
+      <c r="B1981" s="7" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="C1981" s="7" t="inlineStr">
+        <is>
+          <t>WILLOW</t>
+        </is>
+      </c>
+      <c r="D1981" s="7" t="inlineStr">
+        <is>
+          <t>VACANCY_PCT</t>
+        </is>
+      </c>
+      <c r="E1981" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="F1981" s="7" t="n"/>
+      <c r="G1981" s="7" t="inlineStr">
+        <is>
+          <t>Synthetic vacancy percentage example</t>
+        </is>
+      </c>
+      <c r="H1981" s="7" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+    </row>
+    <row r="1982">
+      <c r="A1982" s="12" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B1982" s="7" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="C1982" s="7" t="inlineStr">
+        <is>
+          <t>BEAU</t>
+        </is>
+      </c>
+      <c r="D1982" s="7" t="inlineStr">
+        <is>
+          <t>VACANCY_PCT</t>
+        </is>
+      </c>
+      <c r="E1982" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="F1982" s="7" t="n"/>
+      <c r="G1982" s="7" t="inlineStr">
+        <is>
+          <t>Synthetic vacancy percentage example</t>
+        </is>
+      </c>
+      <c r="H1982" s="7" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+    </row>
+    <row r="1983">
+      <c r="A1983" s="12" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B1983" s="7" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="C1983" s="7" t="inlineStr">
+        <is>
+          <t>BOLD</t>
+        </is>
+      </c>
+      <c r="D1983" s="7" t="inlineStr">
+        <is>
+          <t>VACANCY_PCT</t>
+        </is>
+      </c>
+      <c r="E1983" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="F1983" s="7" t="n"/>
+      <c r="G1983" s="7" t="inlineStr">
+        <is>
+          <t>Synthetic vacancy percentage example</t>
+        </is>
+      </c>
+      <c r="H1983" s="7" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+    </row>
+    <row r="1984">
+      <c r="A1984" s="12" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B1984" s="7" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="C1984" s="7" t="inlineStr">
+        <is>
+          <t>CHELFORD</t>
+        </is>
+      </c>
+      <c r="D1984" s="7" t="inlineStr">
+        <is>
+          <t>VACANCY_PCT</t>
+        </is>
+      </c>
+      <c r="E1984" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="F1984" s="7" t="n"/>
+      <c r="G1984" s="7" t="inlineStr">
+        <is>
+          <t>Synthetic vacancy percentage example</t>
+        </is>
+      </c>
+      <c r="H1984" s="7" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+    </row>
+    <row r="1985">
+      <c r="A1985" s="12" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B1985" s="7" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="C1985" s="7" t="inlineStr">
+        <is>
+          <t>CHURCH</t>
+        </is>
+      </c>
+      <c r="D1985" s="7" t="inlineStr">
+        <is>
+          <t>VACANCY_PCT</t>
+        </is>
+      </c>
+      <c r="E1985" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="F1985" s="7" t="n"/>
+      <c r="G1985" s="7" t="inlineStr">
+        <is>
+          <t>Synthetic vacancy percentage example</t>
+        </is>
+      </c>
+      <c r="H1985" s="7" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+    </row>
+    <row r="1986">
+      <c r="A1986" s="12" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B1986" s="7" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="C1986" s="7" t="inlineStr">
+        <is>
+          <t>HAWKSWORTH</t>
+        </is>
+      </c>
+      <c r="D1986" s="7" t="inlineStr">
+        <is>
+          <t>VACANCY_PCT</t>
+        </is>
+      </c>
+      <c r="E1986" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F1986" s="7" t="n"/>
+      <c r="G1986" s="7" t="inlineStr">
+        <is>
+          <t>Synthetic vacancy percentage example</t>
+        </is>
+      </c>
+      <c r="H1986" s="7" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+    </row>
+    <row r="1987">
+      <c r="A1987" s="12" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B1987" s="7" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="C1987" s="7" t="inlineStr">
+        <is>
+          <t>MILLBROOK</t>
+        </is>
+      </c>
+      <c r="D1987" s="7" t="inlineStr">
+        <is>
+          <t>VACANCY_PCT</t>
+        </is>
+      </c>
+      <c r="E1987" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F1987" s="7" t="n"/>
+      <c r="G1987" s="7" t="inlineStr">
+        <is>
+          <t>Synthetic vacancy percentage example</t>
+        </is>
+      </c>
+      <c r="H1987" s="7" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+    </row>
+    <row r="1988">
+      <c r="A1988" s="12" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B1988" s="7" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="C1988" s="7" t="inlineStr">
+        <is>
+          <t>RAVEN</t>
+        </is>
+      </c>
+      <c r="D1988" s="7" t="inlineStr">
+        <is>
+          <t>VACANCY_PCT</t>
+        </is>
+      </c>
+      <c r="E1988" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="F1988" s="7" t="n"/>
+      <c r="G1988" s="7" t="inlineStr">
+        <is>
+          <t>Synthetic vacancy percentage example</t>
+        </is>
+      </c>
+      <c r="H1988" s="7" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+    </row>
+    <row r="1989">
+      <c r="A1989" s="12" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B1989" s="7" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="C1989" s="7" t="inlineStr">
+        <is>
+          <t>RIVERSIDE</t>
+        </is>
+      </c>
+      <c r="D1989" s="7" t="inlineStr">
+        <is>
+          <t>VACANCY_PCT</t>
+        </is>
+      </c>
+      <c r="E1989" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="F1989" s="7" t="n"/>
+      <c r="G1989" s="7" t="inlineStr">
+        <is>
+          <t>Synthetic vacancy percentage example</t>
+        </is>
+      </c>
+      <c r="H1989" s="7" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+    </row>
+    <row r="1990">
+      <c r="A1990" s="12" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B1990" s="7" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="C1990" s="7" t="inlineStr">
+        <is>
+          <t>RYECROFT</t>
+        </is>
+      </c>
+      <c r="D1990" s="7" t="inlineStr">
+        <is>
+          <t>VACANCY_PCT</t>
+        </is>
+      </c>
+      <c r="E1990" s="7" t="n">
+        <v>14</v>
+      </c>
+      <c r="F1990" s="7" t="n"/>
+      <c r="G1990" s="7" t="inlineStr">
+        <is>
+          <t>Synthetic vacancy percentage example</t>
+        </is>
+      </c>
+      <c r="H1990" s="7" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+    </row>
+    <row r="1991">
+      <c r="A1991" s="12" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B1991" s="7" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="C1991" s="7" t="inlineStr">
+        <is>
+          <t>SEREN</t>
+        </is>
+      </c>
+      <c r="D1991" s="7" t="inlineStr">
+        <is>
+          <t>VACANCY_PCT</t>
+        </is>
+      </c>
+      <c r="E1991" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1991" s="7" t="n"/>
+      <c r="G1991" s="7" t="inlineStr">
+        <is>
+          <t>Synthetic vacancy percentage example</t>
+        </is>
+      </c>
+      <c r="H1991" s="7" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+    </row>
+    <row r="1992">
+      <c r="A1992" s="12" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B1992" s="7" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="C1992" s="7" t="inlineStr">
+        <is>
+          <t>SYCAMORE</t>
+        </is>
+      </c>
+      <c r="D1992" s="7" t="inlineStr">
+        <is>
+          <t>VACANCY_PCT</t>
+        </is>
+      </c>
+      <c r="E1992" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="F1992" s="7" t="n"/>
+      <c r="G1992" s="7" t="inlineStr">
+        <is>
+          <t>Synthetic vacancy percentage example</t>
+        </is>
+      </c>
+      <c r="H1992" s="7" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+    </row>
+    <row r="1993">
+      <c r="A1993" s="12" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B1993" s="7" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="C1993" s="7" t="inlineStr">
+        <is>
+          <t>WILLOW</t>
+        </is>
+      </c>
+      <c r="D1993" s="7" t="inlineStr">
+        <is>
+          <t>VACANCY_PCT</t>
+        </is>
+      </c>
+      <c r="E1993" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="F1993" s="7" t="n"/>
+      <c r="G1993" s="7" t="inlineStr">
+        <is>
+          <t>Synthetic vacancy percentage example</t>
+        </is>
+      </c>
+      <c r="H1993" s="7" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+    </row>
+    <row r="1994">
+      <c r="A1994" s="12" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B1994" s="7" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="C1994" s="7" t="inlineStr">
+        <is>
+          <t>BEAU</t>
+        </is>
+      </c>
+      <c r="D1994" s="7" t="inlineStr">
+        <is>
+          <t>VACANCY_PCT</t>
+        </is>
+      </c>
+      <c r="E1994" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F1994" s="7" t="n"/>
+      <c r="G1994" s="7" t="inlineStr">
+        <is>
+          <t>Synthetic vacancy percentage example</t>
+        </is>
+      </c>
+      <c r="H1994" s="7" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+    </row>
+    <row r="1995">
+      <c r="A1995" s="12" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B1995" s="7" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="C1995" s="7" t="inlineStr">
+        <is>
+          <t>BOLD</t>
+        </is>
+      </c>
+      <c r="D1995" s="7" t="inlineStr">
+        <is>
+          <t>VACANCY_PCT</t>
+        </is>
+      </c>
+      <c r="E1995" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="F1995" s="7" t="n"/>
+      <c r="G1995" s="7" t="inlineStr">
+        <is>
+          <t>Synthetic vacancy percentage example</t>
+        </is>
+      </c>
+      <c r="H1995" s="7" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+    </row>
+    <row r="1996">
+      <c r="A1996" s="12" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B1996" s="7" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="C1996" s="7" t="inlineStr">
+        <is>
+          <t>CHELFORD</t>
+        </is>
+      </c>
+      <c r="D1996" s="7" t="inlineStr">
+        <is>
+          <t>VACANCY_PCT</t>
+        </is>
+      </c>
+      <c r="E1996" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="F1996" s="7" t="n"/>
+      <c r="G1996" s="7" t="inlineStr">
+        <is>
+          <t>Synthetic vacancy percentage example</t>
+        </is>
+      </c>
+      <c r="H1996" s="7" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+    </row>
+    <row r="1997">
+      <c r="A1997" s="12" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B1997" s="7" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="C1997" s="7" t="inlineStr">
+        <is>
+          <t>CHURCH</t>
+        </is>
+      </c>
+      <c r="D1997" s="7" t="inlineStr">
+        <is>
+          <t>VACANCY_PCT</t>
+        </is>
+      </c>
+      <c r="E1997" s="7" t="n">
+        <v>14</v>
+      </c>
+      <c r="F1997" s="7" t="n"/>
+      <c r="G1997" s="7" t="inlineStr">
+        <is>
+          <t>Synthetic vacancy percentage example</t>
+        </is>
+      </c>
+      <c r="H1997" s="7" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+    </row>
+    <row r="1998">
+      <c r="A1998" s="12" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B1998" s="7" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="C1998" s="7" t="inlineStr">
+        <is>
+          <t>HAWKSWORTH</t>
+        </is>
+      </c>
+      <c r="D1998" s="7" t="inlineStr">
+        <is>
+          <t>VACANCY_PCT</t>
+        </is>
+      </c>
+      <c r="E1998" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1998" s="7" t="n"/>
+      <c r="G1998" s="7" t="inlineStr">
+        <is>
+          <t>Synthetic vacancy percentage example</t>
+        </is>
+      </c>
+      <c r="H1998" s="7" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+    </row>
+    <row r="1999">
+      <c r="A1999" s="12" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B1999" s="7" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="C1999" s="7" t="inlineStr">
+        <is>
+          <t>MILLBROOK</t>
+        </is>
+      </c>
+      <c r="D1999" s="7" t="inlineStr">
+        <is>
+          <t>VACANCY_PCT</t>
+        </is>
+      </c>
+      <c r="E1999" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="F1999" s="7" t="n"/>
+      <c r="G1999" s="7" t="inlineStr">
+        <is>
+          <t>Synthetic vacancy percentage example</t>
+        </is>
+      </c>
+      <c r="H1999" s="7" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+    </row>
+    <row r="2000">
+      <c r="A2000" s="12" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B2000" s="7" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="C2000" s="7" t="inlineStr">
+        <is>
+          <t>RAVEN</t>
+        </is>
+      </c>
+      <c r="D2000" s="7" t="inlineStr">
+        <is>
+          <t>VACANCY_PCT</t>
+        </is>
+      </c>
+      <c r="E2000" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="F2000" s="7" t="n"/>
+      <c r="G2000" s="7" t="inlineStr">
+        <is>
+          <t>Synthetic vacancy percentage example</t>
+        </is>
+      </c>
+      <c r="H2000" s="7" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+    </row>
+    <row r="2001">
+      <c r="A2001" s="12" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B2001" s="7" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="C2001" s="7" t="inlineStr">
+        <is>
+          <t>RIVERSIDE</t>
+        </is>
+      </c>
+      <c r="D2001" s="7" t="inlineStr">
+        <is>
+          <t>VACANCY_PCT</t>
+        </is>
+      </c>
+      <c r="E2001" s="7" t="n">
+        <v>13</v>
+      </c>
+      <c r="F2001" s="7" t="n"/>
+      <c r="G2001" s="7" t="inlineStr">
+        <is>
+          <t>Synthetic vacancy percentage example</t>
+        </is>
+      </c>
+      <c r="H2001" s="7" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+    </row>
+    <row r="2002">
+      <c r="A2002" s="12" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B2002" s="7" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="C2002" s="7" t="inlineStr">
+        <is>
+          <t>RYECROFT</t>
+        </is>
+      </c>
+      <c r="D2002" s="7" t="inlineStr">
+        <is>
+          <t>VACANCY_PCT</t>
+        </is>
+      </c>
+      <c r="E2002" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="F2002" s="7" t="n"/>
+      <c r="G2002" s="7" t="inlineStr">
+        <is>
+          <t>Synthetic vacancy percentage example</t>
+        </is>
+      </c>
+      <c r="H2002" s="7" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+    </row>
+    <row r="2003">
+      <c r="A2003" s="12" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B2003" s="7" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="C2003" s="7" t="inlineStr">
+        <is>
+          <t>SEREN</t>
+        </is>
+      </c>
+      <c r="D2003" s="7" t="inlineStr">
+        <is>
+          <t>VACANCY_PCT</t>
+        </is>
+      </c>
+      <c r="E2003" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="F2003" s="7" t="n"/>
+      <c r="G2003" s="7" t="inlineStr">
+        <is>
+          <t>Synthetic vacancy percentage example</t>
+        </is>
+      </c>
+      <c r="H2003" s="7" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+    </row>
+    <row r="2004">
+      <c r="A2004" s="12" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B2004" s="7" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="C2004" s="7" t="inlineStr">
+        <is>
+          <t>SYCAMORE</t>
+        </is>
+      </c>
+      <c r="D2004" s="7" t="inlineStr">
+        <is>
+          <t>VACANCY_PCT</t>
+        </is>
+      </c>
+      <c r="E2004" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="F2004" s="7" t="n"/>
+      <c r="G2004" s="7" t="inlineStr">
+        <is>
+          <t>Synthetic vacancy percentage example</t>
+        </is>
+      </c>
+      <c r="H2004" s="7" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+    </row>
+    <row r="2005">
+      <c r="A2005" s="12" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B2005" s="7" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="C2005" s="7" t="inlineStr">
+        <is>
+          <t>WILLOW</t>
+        </is>
+      </c>
+      <c r="D2005" s="7" t="inlineStr">
+        <is>
+          <t>VACANCY_PCT</t>
+        </is>
+      </c>
+      <c r="E2005" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="F2005" s="7" t="n"/>
+      <c r="G2005" s="7" t="inlineStr">
+        <is>
+          <t>Synthetic vacancy percentage example</t>
+        </is>
+      </c>
+      <c r="H2005" s="7" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+    </row>
+    <row r="2006">
+      <c r="A2006" s="12" t="n">
+        <v>46174</v>
+      </c>
+      <c r="B2006" s="7" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="C2006" s="7" t="inlineStr">
+        <is>
+          <t>BEAU</t>
+        </is>
+      </c>
+      <c r="D2006" s="7" t="inlineStr">
+        <is>
+          <t>VACANCY_PCT</t>
+        </is>
+      </c>
+      <c r="E2006" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="F2006" s="7" t="n"/>
+      <c r="G2006" s="7" t="inlineStr">
+        <is>
+          <t>Synthetic vacancy percentage example</t>
+        </is>
+      </c>
+      <c r="H2006" s="7" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+    </row>
+    <row r="2007">
+      <c r="A2007" s="12" t="n">
+        <v>46174</v>
+      </c>
+      <c r="B2007" s="7" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="C2007" s="7" t="inlineStr">
+        <is>
+          <t>BOLD</t>
+        </is>
+      </c>
+      <c r="D2007" s="7" t="inlineStr">
+        <is>
+          <t>VACANCY_PCT</t>
+        </is>
+      </c>
+      <c r="E2007" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="F2007" s="7" t="n"/>
+      <c r="G2007" s="7" t="inlineStr">
+        <is>
+          <t>Synthetic vacancy percentage example</t>
+        </is>
+      </c>
+      <c r="H2007" s="7" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+    </row>
+    <row r="2008">
+      <c r="A2008" s="12" t="n">
+        <v>46174</v>
+      </c>
+      <c r="B2008" s="7" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="C2008" s="7" t="inlineStr">
+        <is>
+          <t>CHELFORD</t>
+        </is>
+      </c>
+      <c r="D2008" s="7" t="inlineStr">
+        <is>
+          <t>VACANCY_PCT</t>
+        </is>
+      </c>
+      <c r="E2008" s="7" t="n">
+        <v>13</v>
+      </c>
+      <c r="F2008" s="7" t="n"/>
+      <c r="G2008" s="7" t="inlineStr">
+        <is>
+          <t>Synthetic vacancy percentage example</t>
+        </is>
+      </c>
+      <c r="H2008" s="7" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+    </row>
+    <row r="2009">
+      <c r="A2009" s="12" t="n">
+        <v>46174</v>
+      </c>
+      <c r="B2009" s="7" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="C2009" s="7" t="inlineStr">
+        <is>
+          <t>CHURCH</t>
+        </is>
+      </c>
+      <c r="D2009" s="7" t="inlineStr">
+        <is>
+          <t>VACANCY_PCT</t>
+        </is>
+      </c>
+      <c r="E2009" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="F2009" s="7" t="n"/>
+      <c r="G2009" s="7" t="inlineStr">
+        <is>
+          <t>Synthetic vacancy percentage example</t>
+        </is>
+      </c>
+      <c r="H2009" s="7" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+    </row>
+    <row r="2010">
+      <c r="A2010" s="12" t="n">
+        <v>46174</v>
+      </c>
+      <c r="B2010" s="7" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="C2010" s="7" t="inlineStr">
+        <is>
+          <t>HAWKSWORTH</t>
+        </is>
+      </c>
+      <c r="D2010" s="7" t="inlineStr">
+        <is>
+          <t>VACANCY_PCT</t>
+        </is>
+      </c>
+      <c r="E2010" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="F2010" s="7" t="n"/>
+      <c r="G2010" s="7" t="inlineStr">
+        <is>
+          <t>Synthetic vacancy percentage example</t>
+        </is>
+      </c>
+      <c r="H2010" s="7" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+    </row>
+    <row r="2011">
+      <c r="A2011" s="12" t="n">
+        <v>46174</v>
+      </c>
+      <c r="B2011" s="7" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="C2011" s="7" t="inlineStr">
+        <is>
+          <t>MILLBROOK</t>
+        </is>
+      </c>
+      <c r="D2011" s="7" t="inlineStr">
+        <is>
+          <t>VACANCY_PCT</t>
+        </is>
+      </c>
+      <c r="E2011" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="F2011" s="7" t="n"/>
+      <c r="G2011" s="7" t="inlineStr">
+        <is>
+          <t>Synthetic vacancy percentage example</t>
+        </is>
+      </c>
+      <c r="H2011" s="7" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+    </row>
+    <row r="2012">
+      <c r="A2012" s="12" t="n">
+        <v>46174</v>
+      </c>
+      <c r="B2012" s="7" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="C2012" s="7" t="inlineStr">
+        <is>
+          <t>RAVEN</t>
+        </is>
+      </c>
+      <c r="D2012" s="7" t="inlineStr">
+        <is>
+          <t>VACANCY_PCT</t>
+        </is>
+      </c>
+      <c r="E2012" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="F2012" s="7" t="n"/>
+      <c r="G2012" s="7" t="inlineStr">
+        <is>
+          <t>Synthetic vacancy percentage example</t>
+        </is>
+      </c>
+      <c r="H2012" s="7" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+    </row>
+    <row r="2013">
+      <c r="A2013" s="12" t="n">
+        <v>46174</v>
+      </c>
+      <c r="B2013" s="7" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="C2013" s="7" t="inlineStr">
+        <is>
+          <t>RIVERSIDE</t>
+        </is>
+      </c>
+      <c r="D2013" s="7" t="inlineStr">
+        <is>
+          <t>VACANCY_PCT</t>
+        </is>
+      </c>
+      <c r="E2013" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F2013" s="7" t="n"/>
+      <c r="G2013" s="7" t="inlineStr">
+        <is>
+          <t>Synthetic vacancy percentage example</t>
+        </is>
+      </c>
+      <c r="H2013" s="7" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+    </row>
+    <row r="2014">
+      <c r="A2014" s="12" t="n">
+        <v>46174</v>
+      </c>
+      <c r="B2014" s="7" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="C2014" s="7" t="inlineStr">
+        <is>
+          <t>RYECROFT</t>
+        </is>
+      </c>
+      <c r="D2014" s="7" t="inlineStr">
+        <is>
+          <t>VACANCY_PCT</t>
+        </is>
+      </c>
+      <c r="E2014" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F2014" s="7" t="n"/>
+      <c r="G2014" s="7" t="inlineStr">
+        <is>
+          <t>Synthetic vacancy percentage example</t>
+        </is>
+      </c>
+      <c r="H2014" s="7" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+    </row>
+    <row r="2015">
+      <c r="A2015" s="12" t="n">
+        <v>46174</v>
+      </c>
+      <c r="B2015" s="7" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="C2015" s="7" t="inlineStr">
+        <is>
+          <t>SEREN</t>
+        </is>
+      </c>
+      <c r="D2015" s="7" t="inlineStr">
+        <is>
+          <t>VACANCY_PCT</t>
+        </is>
+      </c>
+      <c r="E2015" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="F2015" s="7" t="n"/>
+      <c r="G2015" s="7" t="inlineStr">
+        <is>
+          <t>Synthetic vacancy percentage example</t>
+        </is>
+      </c>
+      <c r="H2015" s="7" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+    </row>
+    <row r="2016">
+      <c r="A2016" s="12" t="n">
+        <v>46174</v>
+      </c>
+      <c r="B2016" s="7" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="C2016" s="7" t="inlineStr">
+        <is>
+          <t>SYCAMORE</t>
+        </is>
+      </c>
+      <c r="D2016" s="7" t="inlineStr">
+        <is>
+          <t>VACANCY_PCT</t>
+        </is>
+      </c>
+      <c r="E2016" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="F2016" s="7" t="n"/>
+      <c r="G2016" s="7" t="inlineStr">
+        <is>
+          <t>Synthetic vacancy percentage example</t>
+        </is>
+      </c>
+      <c r="H2016" s="7" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+    </row>
+    <row r="2017">
+      <c r="A2017" s="12" t="n">
+        <v>46174</v>
+      </c>
+      <c r="B2017" s="7" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="C2017" s="7" t="inlineStr">
+        <is>
+          <t>WILLOW</t>
+        </is>
+      </c>
+      <c r="D2017" s="7" t="inlineStr">
+        <is>
+          <t>VACANCY_PCT</t>
+        </is>
+      </c>
+      <c r="E2017" s="7" t="n">
+        <v>14</v>
+      </c>
+      <c r="F2017" s="7" t="n"/>
+      <c r="G2017" s="7" t="inlineStr">
+        <is>
+          <t>Synthetic vacancy percentage example</t>
+        </is>
+      </c>
+      <c r="H2017" s="7" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+    </row>
+    <row r="2018">
+      <c r="A2018" s="12" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B2018" s="7" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="C2018" s="7" t="inlineStr">
+        <is>
+          <t>BEAU</t>
+        </is>
+      </c>
+      <c r="D2018" s="7" t="inlineStr">
+        <is>
+          <t>VACANCY_PCT</t>
+        </is>
+      </c>
+      <c r="E2018" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="F2018" s="7" t="n"/>
+      <c r="G2018" s="7" t="inlineStr">
+        <is>
+          <t>Synthetic vacancy percentage example</t>
+        </is>
+      </c>
+      <c r="H2018" s="7" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+    </row>
+    <row r="2019">
+      <c r="A2019" s="12" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B2019" s="7" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="C2019" s="7" t="inlineStr">
+        <is>
+          <t>BOLD</t>
+        </is>
+      </c>
+      <c r="D2019" s="7" t="inlineStr">
+        <is>
+          <t>VACANCY_PCT</t>
+        </is>
+      </c>
+      <c r="E2019" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="F2019" s="7" t="n"/>
+      <c r="G2019" s="7" t="inlineStr">
+        <is>
+          <t>Synthetic vacancy percentage example</t>
+        </is>
+      </c>
+      <c r="H2019" s="7" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+    </row>
+    <row r="2020">
+      <c r="A2020" s="12" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B2020" s="7" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="C2020" s="7" t="inlineStr">
+        <is>
+          <t>CHELFORD</t>
+        </is>
+      </c>
+      <c r="D2020" s="7" t="inlineStr">
+        <is>
+          <t>VACANCY_PCT</t>
+        </is>
+      </c>
+      <c r="E2020" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F2020" s="7" t="n"/>
+      <c r="G2020" s="7" t="inlineStr">
+        <is>
+          <t>Synthetic vacancy percentage example</t>
+        </is>
+      </c>
+      <c r="H2020" s="7" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+    </row>
+    <row r="2021">
+      <c r="A2021" s="12" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B2021" s="7" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="C2021" s="7" t="inlineStr">
+        <is>
+          <t>CHURCH</t>
+        </is>
+      </c>
+      <c r="D2021" s="7" t="inlineStr">
+        <is>
+          <t>VACANCY_PCT</t>
+        </is>
+      </c>
+      <c r="E2021" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F2021" s="7" t="n"/>
+      <c r="G2021" s="7" t="inlineStr">
+        <is>
+          <t>Synthetic vacancy percentage example</t>
+        </is>
+      </c>
+      <c r="H2021" s="7" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+    </row>
+    <row r="2022">
+      <c r="A2022" s="12" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B2022" s="7" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="C2022" s="7" t="inlineStr">
+        <is>
+          <t>HAWKSWORTH</t>
+        </is>
+      </c>
+      <c r="D2022" s="7" t="inlineStr">
+        <is>
+          <t>VACANCY_PCT</t>
+        </is>
+      </c>
+      <c r="E2022" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="F2022" s="7" t="n"/>
+      <c r="G2022" s="7" t="inlineStr">
+        <is>
+          <t>Synthetic vacancy percentage example</t>
+        </is>
+      </c>
+      <c r="H2022" s="7" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+    </row>
+    <row r="2023">
+      <c r="A2023" s="12" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B2023" s="7" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="C2023" s="7" t="inlineStr">
+        <is>
+          <t>MILLBROOK</t>
+        </is>
+      </c>
+      <c r="D2023" s="7" t="inlineStr">
+        <is>
+          <t>VACANCY_PCT</t>
+        </is>
+      </c>
+      <c r="E2023" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="F2023" s="7" t="n"/>
+      <c r="G2023" s="7" t="inlineStr">
+        <is>
+          <t>Synthetic vacancy percentage example</t>
+        </is>
+      </c>
+      <c r="H2023" s="7" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+    </row>
+    <row r="2024">
+      <c r="A2024" s="12" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B2024" s="7" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="C2024" s="7" t="inlineStr">
+        <is>
+          <t>RAVEN</t>
+        </is>
+      </c>
+      <c r="D2024" s="7" t="inlineStr">
+        <is>
+          <t>VACANCY_PCT</t>
+        </is>
+      </c>
+      <c r="E2024" s="7" t="n">
+        <v>14</v>
+      </c>
+      <c r="F2024" s="7" t="n"/>
+      <c r="G2024" s="7" t="inlineStr">
+        <is>
+          <t>Synthetic vacancy percentage example</t>
+        </is>
+      </c>
+      <c r="H2024" s="7" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+    </row>
+    <row r="2025">
+      <c r="A2025" s="12" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B2025" s="7" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="C2025" s="7" t="inlineStr">
+        <is>
+          <t>RIVERSIDE</t>
+        </is>
+      </c>
+      <c r="D2025" s="7" t="inlineStr">
+        <is>
+          <t>VACANCY_PCT</t>
+        </is>
+      </c>
+      <c r="E2025" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="F2025" s="7" t="n"/>
+      <c r="G2025" s="7" t="inlineStr">
+        <is>
+          <t>Synthetic vacancy percentage example</t>
+        </is>
+      </c>
+      <c r="H2025" s="7" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+    </row>
+    <row r="2026">
+      <c r="A2026" s="12" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B2026" s="7" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="C2026" s="7" t="inlineStr">
+        <is>
+          <t>RYECROFT</t>
+        </is>
+      </c>
+      <c r="D2026" s="7" t="inlineStr">
+        <is>
+          <t>VACANCY_PCT</t>
+        </is>
+      </c>
+      <c r="E2026" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="F2026" s="7" t="n"/>
+      <c r="G2026" s="7" t="inlineStr">
+        <is>
+          <t>Synthetic vacancy percentage example</t>
+        </is>
+      </c>
+      <c r="H2026" s="7" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+    </row>
+    <row r="2027">
+      <c r="A2027" s="12" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B2027" s="7" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="C2027" s="7" t="inlineStr">
+        <is>
+          <t>SEREN</t>
+        </is>
+      </c>
+      <c r="D2027" s="7" t="inlineStr">
+        <is>
+          <t>VACANCY_PCT</t>
+        </is>
+      </c>
+      <c r="E2027" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="F2027" s="7" t="n"/>
+      <c r="G2027" s="7" t="inlineStr">
+        <is>
+          <t>Synthetic vacancy percentage example</t>
+        </is>
+      </c>
+      <c r="H2027" s="7" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+    </row>
+    <row r="2028">
+      <c r="A2028" s="12" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B2028" s="7" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="C2028" s="7" t="inlineStr">
+        <is>
+          <t>SYCAMORE</t>
+        </is>
+      </c>
+      <c r="D2028" s="7" t="inlineStr">
+        <is>
+          <t>VACANCY_PCT</t>
+        </is>
+      </c>
+      <c r="E2028" s="7" t="n">
+        <v>13</v>
+      </c>
+      <c r="F2028" s="7" t="n"/>
+      <c r="G2028" s="7" t="inlineStr">
+        <is>
+          <t>Synthetic vacancy percentage example</t>
+        </is>
+      </c>
+      <c r="H2028" s="7" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+    </row>
+    <row r="2029">
+      <c r="A2029" s="12" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B2029" s="7" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="C2029" s="7" t="inlineStr">
+        <is>
+          <t>WILLOW</t>
+        </is>
+      </c>
+      <c r="D2029" s="7" t="inlineStr">
+        <is>
+          <t>VACANCY_PCT</t>
+        </is>
+      </c>
+      <c r="E2029" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="F2029" s="7" t="n"/>
+      <c r="G2029" s="7" t="inlineStr">
+        <is>
+          <t>Synthetic vacancy percentage example</t>
+        </is>
+      </c>
+      <c r="H2029" s="7" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+    </row>
+    <row r="2030">
+      <c r="A2030" s="12" t="n">
+        <v>46235</v>
+      </c>
+      <c r="B2030" s="7" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="C2030" s="7" t="inlineStr">
+        <is>
+          <t>BEAU</t>
+        </is>
+      </c>
+      <c r="D2030" s="7" t="inlineStr">
+        <is>
+          <t>VACANCY_PCT</t>
+        </is>
+      </c>
+      <c r="E2030" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="F2030" s="7" t="n"/>
+      <c r="G2030" s="7" t="inlineStr">
+        <is>
+          <t>Synthetic vacancy percentage example</t>
+        </is>
+      </c>
+      <c r="H2030" s="7" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+    </row>
+    <row r="2031">
+      <c r="A2031" s="12" t="n">
+        <v>46235</v>
+      </c>
+      <c r="B2031" s="7" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="C2031" s="7" t="inlineStr">
+        <is>
+          <t>BOLD</t>
+        </is>
+      </c>
+      <c r="D2031" s="7" t="inlineStr">
+        <is>
+          <t>VACANCY_PCT</t>
+        </is>
+      </c>
+      <c r="E2031" s="7" t="n">
+        <v>14</v>
+      </c>
+      <c r="F2031" s="7" t="n"/>
+      <c r="G2031" s="7" t="inlineStr">
+        <is>
+          <t>Synthetic vacancy percentage example</t>
+        </is>
+      </c>
+      <c r="H2031" s="7" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+    </row>
+    <row r="2032">
+      <c r="A2032" s="12" t="n">
+        <v>46235</v>
+      </c>
+      <c r="B2032" s="7" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="C2032" s="7" t="inlineStr">
+        <is>
+          <t>CHELFORD</t>
+        </is>
+      </c>
+      <c r="D2032" s="7" t="inlineStr">
+        <is>
+          <t>VACANCY_PCT</t>
+        </is>
+      </c>
+      <c r="E2032" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="F2032" s="7" t="n"/>
+      <c r="G2032" s="7" t="inlineStr">
+        <is>
+          <t>Synthetic vacancy percentage example</t>
+        </is>
+      </c>
+      <c r="H2032" s="7" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+    </row>
+    <row r="2033">
+      <c r="A2033" s="12" t="n">
+        <v>46235</v>
+      </c>
+      <c r="B2033" s="7" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="C2033" s="7" t="inlineStr">
+        <is>
+          <t>CHURCH</t>
+        </is>
+      </c>
+      <c r="D2033" s="7" t="inlineStr">
+        <is>
+          <t>VACANCY_PCT</t>
+        </is>
+      </c>
+      <c r="E2033" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="F2033" s="7" t="n"/>
+      <c r="G2033" s="7" t="inlineStr">
+        <is>
+          <t>Synthetic vacancy percentage example</t>
+        </is>
+      </c>
+      <c r="H2033" s="7" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+    </row>
+    <row r="2034">
+      <c r="A2034" s="12" t="n">
+        <v>46235</v>
+      </c>
+      <c r="B2034" s="7" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="C2034" s="7" t="inlineStr">
+        <is>
+          <t>HAWKSWORTH</t>
+        </is>
+      </c>
+      <c r="D2034" s="7" t="inlineStr">
+        <is>
+          <t>VACANCY_PCT</t>
+        </is>
+      </c>
+      <c r="E2034" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="F2034" s="7" t="n"/>
+      <c r="G2034" s="7" t="inlineStr">
+        <is>
+          <t>Synthetic vacancy percentage example</t>
+        </is>
+      </c>
+      <c r="H2034" s="7" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+    </row>
+    <row r="2035">
+      <c r="A2035" s="12" t="n">
+        <v>46235</v>
+      </c>
+      <c r="B2035" s="7" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="C2035" s="7" t="inlineStr">
+        <is>
+          <t>MILLBROOK</t>
+        </is>
+      </c>
+      <c r="D2035" s="7" t="inlineStr">
+        <is>
+          <t>VACANCY_PCT</t>
+        </is>
+      </c>
+      <c r="E2035" s="7" t="n">
+        <v>13</v>
+      </c>
+      <c r="F2035" s="7" t="n"/>
+      <c r="G2035" s="7" t="inlineStr">
+        <is>
+          <t>Synthetic vacancy percentage example</t>
+        </is>
+      </c>
+      <c r="H2035" s="7" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+    </row>
+    <row r="2036">
+      <c r="A2036" s="12" t="n">
+        <v>46235</v>
+      </c>
+      <c r="B2036" s="7" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="C2036" s="7" t="inlineStr">
+        <is>
+          <t>RAVEN</t>
+        </is>
+      </c>
+      <c r="D2036" s="7" t="inlineStr">
+        <is>
+          <t>VACANCY_PCT</t>
+        </is>
+      </c>
+      <c r="E2036" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="F2036" s="7" t="n"/>
+      <c r="G2036" s="7" t="inlineStr">
+        <is>
+          <t>Synthetic vacancy percentage example</t>
+        </is>
+      </c>
+      <c r="H2036" s="7" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+    </row>
+    <row r="2037">
+      <c r="A2037" s="12" t="n">
+        <v>46235</v>
+      </c>
+      <c r="B2037" s="7" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="C2037" s="7" t="inlineStr">
+        <is>
+          <t>RIVERSIDE</t>
+        </is>
+      </c>
+      <c r="D2037" s="7" t="inlineStr">
+        <is>
+          <t>VACANCY_PCT</t>
+        </is>
+      </c>
+      <c r="E2037" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="F2037" s="7" t="n"/>
+      <c r="G2037" s="7" t="inlineStr">
+        <is>
+          <t>Synthetic vacancy percentage example</t>
+        </is>
+      </c>
+      <c r="H2037" s="7" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+    </row>
+    <row r="2038">
+      <c r="A2038" s="12" t="n">
+        <v>46235</v>
+      </c>
+      <c r="B2038" s="7" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="C2038" s="7" t="inlineStr">
+        <is>
+          <t>RYECROFT</t>
+        </is>
+      </c>
+      <c r="D2038" s="7" t="inlineStr">
+        <is>
+          <t>VACANCY_PCT</t>
+        </is>
+      </c>
+      <c r="E2038" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="F2038" s="7" t="n"/>
+      <c r="G2038" s="7" t="inlineStr">
+        <is>
+          <t>Synthetic vacancy percentage example</t>
+        </is>
+      </c>
+      <c r="H2038" s="7" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+    </row>
+    <row r="2039">
+      <c r="A2039" s="12" t="n">
+        <v>46235</v>
+      </c>
+      <c r="B2039" s="7" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="C2039" s="7" t="inlineStr">
+        <is>
+          <t>SEREN</t>
+        </is>
+      </c>
+      <c r="D2039" s="7" t="inlineStr">
+        <is>
+          <t>VACANCY_PCT</t>
+        </is>
+      </c>
+      <c r="E2039" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="F2039" s="7" t="n"/>
+      <c r="G2039" s="7" t="inlineStr">
+        <is>
+          <t>Synthetic vacancy percentage example</t>
+        </is>
+      </c>
+      <c r="H2039" s="7" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+    </row>
+    <row r="2040">
+      <c r="A2040" s="12" t="n">
+        <v>46235</v>
+      </c>
+      <c r="B2040" s="7" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="C2040" s="7" t="inlineStr">
+        <is>
+          <t>SYCAMORE</t>
+        </is>
+      </c>
+      <c r="D2040" s="7" t="inlineStr">
+        <is>
+          <t>VACANCY_PCT</t>
+        </is>
+      </c>
+      <c r="E2040" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F2040" s="7" t="n"/>
+      <c r="G2040" s="7" t="inlineStr">
+        <is>
+          <t>Synthetic vacancy percentage example</t>
+        </is>
+      </c>
+      <c r="H2040" s="7" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+    </row>
+    <row r="2041">
+      <c r="A2041" s="12" t="n">
+        <v>46235</v>
+      </c>
+      <c r="B2041" s="7" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="C2041" s="7" t="inlineStr">
+        <is>
+          <t>WILLOW</t>
+        </is>
+      </c>
+      <c r="D2041" s="7" t="inlineStr">
+        <is>
+          <t>VACANCY_PCT</t>
+        </is>
+      </c>
+      <c r="E2041" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F2041" s="7" t="n"/>
+      <c r="G2041" s="7" t="inlineStr">
+        <is>
+          <t>Synthetic vacancy percentage example</t>
+        </is>
+      </c>
+      <c r="H2041" s="7" t="inlineStr">
         <is>
           <t>People</t>
         </is>
@@ -60022,7 +64930,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -60491,17 +65399,17 @@
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>OCCUPANCY</t>
+          <t>VACANCY_PCT</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>Occupancy</t>
+          <t>Vacancies %</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>Operations</t>
+          <t>People</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
@@ -60511,35 +65419,35 @@
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>Higher is better</t>
+          <t>Lower is better</t>
         </is>
       </c>
       <c r="F12" s="7" t="n"/>
       <c r="G12" s="7" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I12" s="7" t="inlineStr">
         <is>
-          <t>Group only; example threshold only</t>
+          <t>Starter thresholds: Green &lt;= 5%; Amber &gt; 5% to 10%; Red &gt; 10%. Configurable in KPI Setup.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>HOURS_USAGE</t>
+          <t>OCCUPANCY</t>
         </is>
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>Hours Usage</t>
+          <t>Occupancy</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
@@ -60554,38 +65462,40 @@
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
-          <t>Target Range</t>
-        </is>
-      </c>
-      <c r="F13" s="7" t="n">
-        <v>100</v>
-      </c>
-      <c r="G13" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="H13" s="7" t="n">
-        <v>5</v>
+          <t>Higher is better</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="n"/>
+      <c r="G13" s="7" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="H13" s="7" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
       </c>
       <c r="I13" s="7" t="inlineStr">
         <is>
-          <t>Target 100%. Green within +/-2%; Amber within +/-5%; Red outside +/-5%.</t>
+          <t>Group only; example threshold only</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>BUDGET_VARIANCE</t>
+          <t>HOURS_USAGE</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Budget Over / Underspend</t>
+          <t>Hours Usage</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
@@ -60599,7 +65509,7 @@
         </is>
       </c>
       <c r="F14" s="7" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G14" s="7" t="n">
         <v>2</v>
@@ -60609,48 +65519,89 @@
       </c>
       <c r="I14" s="7" t="inlineStr">
         <is>
-          <t>Target 0%. Green within +/-2%; Amber within +/-5%; Red outside +/-5%.</t>
+          <t>Target 100%. Green within +/-2%; Amber within +/-5%; Red outside +/-5%.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
         <is>
+          <t>BUDGET_VARIANCE</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>Budget Over / Underspend</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>Target Range</t>
+        </is>
+      </c>
+      <c r="F15" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="H15" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="I15" s="7" t="inlineStr">
+        <is>
+          <t>Target 0%. Green within +/-2%; Amber within +/-5%; Red outside +/-5%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
           <t>NPS_SCORE</t>
         </is>
       </c>
-      <c r="B15" s="7" t="inlineStr">
+      <c r="B16" s="7" t="inlineStr">
         <is>
           <t>NPS Score</t>
         </is>
       </c>
-      <c r="C15" s="7" t="inlineStr">
+      <c r="C16" s="7" t="inlineStr">
         <is>
           <t>People</t>
         </is>
       </c>
-      <c r="D15" s="7" t="inlineStr">
+      <c r="D16" s="7" t="inlineStr">
         <is>
           <t>Score</t>
         </is>
       </c>
-      <c r="E15" s="7" t="inlineStr">
+      <c r="E16" s="7" t="inlineStr">
         <is>
           <t>Higher is better</t>
         </is>
       </c>
-      <c r="F15" s="7" t="n"/>
-      <c r="G15" s="7" t="inlineStr">
+      <c r="F16" s="7" t="n"/>
+      <c r="G16" s="7" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="H15" s="7" t="inlineStr">
+      <c r="H16" s="7" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="I15" s="7" t="inlineStr">
+      <c r="I16" s="7" t="inlineStr">
         <is>
           <t>Starter thresholds: Green &gt;= 50; Amber 0 to 49.9; Red &lt; 0. Configurable in KPI Setup.</t>
         </is>
